--- a/descstatistics.xlsx
+++ b/descstatistics.xlsx
@@ -679,701 +679,701 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>IPI</t>
         </is>
       </c>
       <c r="B12">
-        <v>125.8768805093046</v>
+        <v>0.001947824668543269</v>
       </c>
       <c r="C12">
-        <v>88.94810439616614</v>
+        <v>0.002664339781292776</v>
       </c>
       <c r="D12">
-        <v>103.1</v>
+        <v>0.001947824668543269</v>
       </c>
       <c r="E12">
-        <v>3.32</v>
+        <v>-0.103433827334549</v>
       </c>
       <c r="F12">
-        <v>861.1</v>
+        <v>0.07405317149206574</v>
       </c>
       <c r="G12">
-        <v>2.370695903486064</v>
+        <v>-12.24642065682345</v>
       </c>
       <c r="H12">
-        <v>8.842968903161186</v>
+        <v>746.9851222140363</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IPI</t>
+          <t>UMP</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.001947824668543269</v>
+        <v>0.00540493374766115</v>
       </c>
       <c r="C13">
-        <v>0.002664339781292776</v>
+        <v>0.03086065312370483</v>
       </c>
       <c r="D13">
-        <v>0.001947824668543269</v>
+        <v>0.00540493374766115</v>
       </c>
       <c r="E13">
-        <v>-0.103433827334549</v>
+        <v>-0.176470588235294</v>
       </c>
       <c r="F13">
-        <v>0.07405317149206574</v>
+        <v>2.34090909090909</v>
       </c>
       <c r="G13">
-        <v>-12.24642065682345</v>
+        <v>70.73369458948586</v>
       </c>
       <c r="H13">
-        <v>746.9851222140363</v>
+        <v>5352.863386482351</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UMP</t>
+          <t>EEPH</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.00540493374766115</v>
+        <v>91.76781538208495</v>
       </c>
       <c r="C14">
-        <v>0.03086065312370483</v>
+        <v>0.7917281122484185</v>
       </c>
       <c r="D14">
-        <v>0.00540493374766115</v>
+        <v>91.76781538208495</v>
       </c>
       <c r="E14">
-        <v>-0.176470588235294</v>
+        <v>74.61604611401472</v>
       </c>
       <c r="F14">
-        <v>2.34090909090909</v>
+        <v>120.608959652287</v>
       </c>
       <c r="G14">
-        <v>70.73369458948586</v>
+        <v>7.876707063092192</v>
       </c>
       <c r="H14">
-        <v>5352.863386482351</v>
+        <v>584.9223233897566</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EEPH</t>
+          <t>TEMP</t>
         </is>
       </c>
       <c r="B15">
-        <v>91.76781538208495</v>
+        <v>0.7095084190368652</v>
       </c>
       <c r="C15">
-        <v>0.7917281122484185</v>
+        <v>0.007400211348411915</v>
       </c>
       <c r="D15">
-        <v>91.76781538208495</v>
+        <v>0.7095084190368652</v>
       </c>
       <c r="E15">
-        <v>74.61604611401472</v>
+        <v>0.4656498432159424</v>
       </c>
       <c r="F15">
-        <v>120.608959652287</v>
+        <v>0.932927131652832</v>
       </c>
       <c r="G15">
-        <v>7.876707063092192</v>
+        <v>1.504342534948598</v>
       </c>
       <c r="H15">
-        <v>584.9223233897566</v>
+        <v>635.189437187361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TEMP</t>
+          <t>co2_per_capita</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.7095084190368652</v>
+        <v>4.74131253361702</v>
       </c>
       <c r="C16">
-        <v>0.007400211348411915</v>
+        <v>0.005528394541957961</v>
       </c>
       <c r="D16">
-        <v>0.7095084190368652</v>
+        <v>4.74131253361702</v>
       </c>
       <c r="E16">
-        <v>0.4656498432159424</v>
+        <v>4.497000217437744</v>
       </c>
       <c r="F16">
-        <v>0.932927131652832</v>
+        <v>4.888000011444092</v>
       </c>
       <c r="G16">
-        <v>1.504342534948598</v>
+        <v>-12.15935685502329</v>
       </c>
       <c r="H16">
-        <v>635.189437187361</v>
+        <v>1024.704864611302</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>co2_per_capita</t>
+          <t>solarpv</t>
         </is>
       </c>
       <c r="B17">
-        <v>4.74131253361702</v>
+        <v>22276.375</v>
       </c>
       <c r="C17">
-        <v>0.005528394541957961</v>
+        <v>493.9586769050584</v>
       </c>
       <c r="D17">
-        <v>4.74131253361702</v>
+        <v>22276.375</v>
       </c>
       <c r="E17">
-        <v>4.497000217437744</v>
+        <v>1453</v>
       </c>
       <c r="F17">
-        <v>4.888000011444092</v>
+        <v>36117</v>
       </c>
       <c r="G17">
-        <v>-12.15935685502329</v>
+        <v>-14.7892201020686</v>
       </c>
       <c r="H17">
-        <v>1024.704864611302</v>
+        <v>977.6665274796063</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>solarpv</t>
+          <t>solarthermal</t>
         </is>
       </c>
       <c r="B18">
-        <v>22276.375</v>
+        <v>7954.0625</v>
       </c>
       <c r="C18">
-        <v>493.9586769050584</v>
+        <v>137.0049895933334</v>
       </c>
       <c r="D18">
-        <v>22276.375</v>
+        <v>7954.0625</v>
       </c>
       <c r="E18">
-        <v>1453</v>
+        <v>449</v>
       </c>
       <c r="F18">
-        <v>36117</v>
+        <v>11170</v>
       </c>
       <c r="G18">
-        <v>-14.7892201020686</v>
+        <v>-26.26711975642949</v>
       </c>
       <c r="H18">
-        <v>977.6665274796063</v>
+        <v>1732.689460132794</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>solarthermal</t>
+          <t>solarpvthermalhybrid</t>
         </is>
       </c>
       <c r="B19">
-        <v>7954.0625</v>
+        <v>2159.875</v>
       </c>
       <c r="C19">
-        <v>137.0049895933334</v>
+        <v>46.8398221471379</v>
       </c>
       <c r="D19">
-        <v>7954.0625</v>
+        <v>2159.875</v>
       </c>
       <c r="E19">
-        <v>449</v>
+        <v>90</v>
       </c>
       <c r="F19">
-        <v>11170</v>
+        <v>3825</v>
       </c>
       <c r="G19">
-        <v>-26.26711975642949</v>
+        <v>-7.565700364620867</v>
       </c>
       <c r="H19">
-        <v>1732.689460132794</v>
+        <v>1058.196909928706</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>solarpvthermalhybrid</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="B20">
-        <v>2159.875</v>
+        <v>9924.6875</v>
       </c>
       <c r="C20">
-        <v>46.8398221471379</v>
+        <v>178.9155693878757</v>
       </c>
       <c r="D20">
-        <v>2159.875</v>
+        <v>9924.6875</v>
       </c>
       <c r="E20">
-        <v>90</v>
+        <v>775</v>
       </c>
       <c r="F20">
-        <v>3825</v>
+        <v>13780</v>
       </c>
       <c r="G20">
-        <v>-7.565700364620867</v>
+        <v>-24.60018216429721</v>
       </c>
       <c r="H20">
-        <v>1058.196909928706</v>
+        <v>1436.581507220444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>hydropower</t>
         </is>
       </c>
       <c r="B21">
-        <v>9924.6875</v>
+        <v>2331.875</v>
       </c>
       <c r="C21">
-        <v>178.9155693878757</v>
+        <v>38.72657000677695</v>
       </c>
       <c r="D21">
-        <v>9924.6875</v>
+        <v>2331.875</v>
       </c>
       <c r="E21">
-        <v>775</v>
+        <v>206</v>
       </c>
       <c r="F21">
-        <v>13780</v>
+        <v>3037</v>
       </c>
       <c r="G21">
-        <v>-24.60018216429721</v>
+        <v>-30.30868058014197</v>
       </c>
       <c r="H21">
-        <v>1436.581507220444</v>
+        <v>1726.114487076653</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hydropower</t>
+          <t>marineandtidal</t>
         </is>
       </c>
       <c r="B22">
-        <v>2331.875</v>
+        <v>1411.4375</v>
       </c>
       <c r="C22">
-        <v>38.72657000677695</v>
+        <v>22.71170133545747</v>
       </c>
       <c r="D22">
-        <v>2331.875</v>
+        <v>1411.4375</v>
       </c>
       <c r="E22">
-        <v>206</v>
+        <v>116</v>
       </c>
       <c r="F22">
-        <v>3037</v>
+        <v>1814</v>
       </c>
       <c r="G22">
-        <v>-30.30868058014197</v>
+        <v>-30.00424012229628</v>
       </c>
       <c r="H22">
-        <v>1726.114487076653</v>
+        <v>1888.965241711528</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>marineandtidal</t>
+          <t>bioenergy</t>
         </is>
       </c>
       <c r="B23">
-        <v>1411.4375</v>
+        <v>7320.375</v>
       </c>
       <c r="C23">
-        <v>22.71170133545747</v>
+        <v>130.4139617854294</v>
       </c>
       <c r="D23">
-        <v>1411.4375</v>
+        <v>7320.375</v>
       </c>
       <c r="E23">
-        <v>116</v>
+        <v>253</v>
       </c>
       <c r="F23">
-        <v>1814</v>
+        <v>9681</v>
       </c>
       <c r="G23">
-        <v>-30.00424012229628</v>
+        <v>-27.04323329357048</v>
       </c>
       <c r="H23">
-        <v>1888.965241711528</v>
+        <v>1619.925495147122</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bioenergy</t>
+          <t>geothermal</t>
         </is>
       </c>
       <c r="B24">
-        <v>7320.375</v>
+        <v>755.625</v>
       </c>
       <c r="C24">
-        <v>130.4139617854294</v>
+        <v>14.86829114702335</v>
       </c>
       <c r="D24">
-        <v>7320.375</v>
+        <v>755.625</v>
       </c>
       <c r="E24">
-        <v>253</v>
+        <v>25</v>
       </c>
       <c r="F24">
-        <v>9681</v>
+        <v>1248</v>
       </c>
       <c r="G24">
-        <v>-27.04323329357048</v>
+        <v>-12.33788482970295</v>
       </c>
       <c r="H24">
-        <v>1619.925495147122</v>
+        <v>1334.211534484704</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>geothermal</t>
+          <t>bioenergyLCOE</t>
         </is>
       </c>
       <c r="B25">
-        <v>755.625</v>
+        <v>0.06962120408813159</v>
       </c>
       <c r="C25">
-        <v>14.86829114702335</v>
+        <v>0.000380129891951757</v>
       </c>
       <c r="D25">
-        <v>755.625</v>
+        <v>0.06962120408813159</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>0.0553603321313858</v>
       </c>
       <c r="F25">
-        <v>1248</v>
+        <v>0.08237511664628983</v>
       </c>
       <c r="G25">
-        <v>-12.33788482970295</v>
+        <v>-2.885864478249564</v>
       </c>
       <c r="H25">
-        <v>1334.211534484704</v>
+        <v>1021.792595257817</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bioenergyLCOE</t>
+          <t>geothermalLCOE</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.06962120408813159</v>
+        <v>0.065447521480647</v>
       </c>
       <c r="C26">
-        <v>0.000380129891951757</v>
+        <v>0.0003733123594546809</v>
       </c>
       <c r="D26">
-        <v>0.06962120408813159</v>
+        <v>0.065447521480647</v>
       </c>
       <c r="E26">
-        <v>0.0553603321313858</v>
+        <v>0.05044528841972351</v>
       </c>
       <c r="F26">
-        <v>0.08237511664628983</v>
+        <v>0.08569453656673431</v>
       </c>
       <c r="G26">
-        <v>-2.885864478249564</v>
+        <v>10.78795156952699</v>
       </c>
       <c r="H26">
-        <v>1021.792595257817</v>
+        <v>1990.893766438241</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>geothermalLCOE</t>
+          <t>offshorewindLCOE</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.065447521480647</v>
+        <v>0.1334782298654318</v>
       </c>
       <c r="C27">
-        <v>0.0003733123594546809</v>
+        <v>0.001843447812742883</v>
       </c>
       <c r="D27">
-        <v>0.065447521480647</v>
+        <v>0.1334782298654318</v>
       </c>
       <c r="E27">
-        <v>0.05044528841972351</v>
+        <v>0.0751669704914093</v>
       </c>
       <c r="F27">
-        <v>0.08569453656673431</v>
+        <v>0.1975487768650055</v>
       </c>
       <c r="G27">
-        <v>10.78795156952699</v>
+        <v>2.197925868578704</v>
       </c>
       <c r="H27">
-        <v>1990.893766438241</v>
+        <v>754.6741312417042</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>offshorewindLCOE</t>
+          <t>solarphotovoltaicLCOE</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.1334782298654318</v>
+        <v>0.1541555915027857</v>
       </c>
       <c r="C28">
-        <v>0.001843447812742883</v>
+        <v>0.004871540717400084</v>
       </c>
       <c r="D28">
-        <v>0.1334782298654318</v>
+        <v>0.1541555915027857</v>
       </c>
       <c r="E28">
-        <v>0.0751669704914093</v>
+        <v>0.04834553971886635</v>
       </c>
       <c r="F28">
-        <v>0.1975487768650055</v>
+        <v>0.4171486794948578</v>
       </c>
       <c r="G28">
-        <v>2.197925868578704</v>
+        <v>26.22890935725088</v>
       </c>
       <c r="H28">
-        <v>754.6741312417042</v>
+        <v>1678.832551711825</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>solarphotovoltaicLCOE</t>
+          <t>concentratedsolarLCOE</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.1541555915027857</v>
+        <v>0.2305581656595071</v>
       </c>
       <c r="C29">
-        <v>0.004871540717400084</v>
+        <v>0.003579862352672162</v>
       </c>
       <c r="D29">
-        <v>0.1541555915027857</v>
+        <v>0.2305581656595071</v>
       </c>
       <c r="E29">
-        <v>0.04834553971886635</v>
+        <v>0.1066529899835587</v>
       </c>
       <c r="F29">
-        <v>0.4171486794948578</v>
+        <v>0.3580037951469421</v>
       </c>
       <c r="G29">
-        <v>26.22890935725088</v>
+        <v>2.955677824349928</v>
       </c>
       <c r="H29">
-        <v>1678.832551711825</v>
+        <v>1030.808683612083</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>concentratedsolarLCOE</t>
+          <t>hydropowerLCOE</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.2305581656595071</v>
+        <v>0.04247033502906561</v>
       </c>
       <c r="C30">
-        <v>0.003579862352672162</v>
+        <v>0.0002058803470562588</v>
       </c>
       <c r="D30">
-        <v>0.2305581656595071</v>
+        <v>0.04247033502906561</v>
       </c>
       <c r="E30">
-        <v>0.1066529899835587</v>
+        <v>0.03656065836548805</v>
       </c>
       <c r="F30">
-        <v>0.3580037951469421</v>
+        <v>0.05072170868515968</v>
       </c>
       <c r="G30">
-        <v>2.955677824349928</v>
+        <v>8.335920960256342</v>
       </c>
       <c r="H30">
-        <v>1030.808683612083</v>
+        <v>923.586105233124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hydropowerLCOE</t>
+          <t>onshorewindLCOE</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.04247033502906561</v>
+        <v>0.06790467258542776</v>
       </c>
       <c r="C31">
-        <v>0.0002058803470562588</v>
+        <v>0.0009962096110690834</v>
       </c>
       <c r="D31">
-        <v>0.04247033502906561</v>
+        <v>0.06790467258542776</v>
       </c>
       <c r="E31">
-        <v>0.03656065836548805</v>
+        <v>0.03312336653470993</v>
       </c>
       <c r="F31">
-        <v>0.05072170868515968</v>
+        <v>0.102061465382576</v>
       </c>
       <c r="G31">
-        <v>8.335920960256342</v>
+        <v>-0.9991611239017049</v>
       </c>
       <c r="H31">
-        <v>923.586105233124</v>
+        <v>854.9708813145097</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>onshorewindLCOE</t>
+          <t>AC_WIND_E</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.06790467258542776</v>
+        <v>305.1769217647059</v>
       </c>
       <c r="C32">
-        <v>0.0009962096110690834</v>
+        <v>8.762659601141614</v>
       </c>
       <c r="D32">
-        <v>0.06790467258542776</v>
+        <v>305.1769217647059</v>
       </c>
       <c r="E32">
-        <v>0.03312336653470993</v>
+        <v>80.27706999999999</v>
       </c>
       <c r="F32">
-        <v>0.102061465382576</v>
+        <v>665.4131</v>
       </c>
       <c r="G32">
-        <v>-0.9991611239017049</v>
+        <v>14.10859149369666</v>
       </c>
       <c r="H32">
-        <v>854.9708813145097</v>
+        <v>988.0960300875448</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AC_WIND_E</t>
+          <t>AC_SOLAR_E</t>
         </is>
       </c>
       <c r="B33">
-        <v>305.1769217647059</v>
+        <v>202.1321261764706</v>
       </c>
       <c r="C33">
-        <v>8.762659601141614</v>
+        <v>10.09321381973508</v>
       </c>
       <c r="D33">
-        <v>305.1769217647059</v>
+        <v>202.1321261764706</v>
       </c>
       <c r="E33">
-        <v>80.27706999999999</v>
+        <v>4.406489</v>
       </c>
       <c r="F33">
-        <v>665.4131</v>
+        <v>676.4082</v>
       </c>
       <c r="G33">
-        <v>14.10859149369666</v>
+        <v>18.58079633804018</v>
       </c>
       <c r="H33">
-        <v>988.0960300875448</v>
+        <v>1102.155273548304</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AC_SOLAR_E</t>
+          <t>AC_HYD_E</t>
         </is>
       </c>
       <c r="B34">
-        <v>202.1321261764706</v>
+        <v>174.3219188235294</v>
       </c>
       <c r="C34">
-        <v>10.09321381973508</v>
+        <v>9.674347097763933</v>
       </c>
       <c r="D34">
-        <v>202.1321261764706</v>
+        <v>174.3219188235294</v>
       </c>
       <c r="E34">
-        <v>4.406489</v>
+        <v>-225.667</v>
       </c>
       <c r="F34">
-        <v>676.4082</v>
+        <v>454.2148</v>
       </c>
       <c r="G34">
-        <v>18.58079633804018</v>
+        <v>-7.788702395170548</v>
       </c>
       <c r="H34">
-        <v>1102.155273548304</v>
+        <v>895.3966891200999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AC_HYD_E</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="B35">
-        <v>174.3219188235294</v>
+        <v>82.74980143178919</v>
       </c>
       <c r="C35">
-        <v>9.674347097763933</v>
+        <v>0.6329777075439798</v>
       </c>
       <c r="D35">
-        <v>174.3219188235294</v>
+        <v>82.74980143178919</v>
       </c>
       <c r="E35">
-        <v>-225.667</v>
+        <v>66.31646700415607</v>
       </c>
       <c r="F35">
-        <v>454.2148</v>
+        <v>100.8155134603174</v>
       </c>
       <c r="G35">
-        <v>-7.788702395170548</v>
+        <v>0.8880139951017569</v>
       </c>
       <c r="H35">
-        <v>895.3966891200999</v>
+        <v>546.0972577444435</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="B36">
-        <v>82.74980143178919</v>
+        <v>125.8768805093046</v>
       </c>
       <c r="C36">
-        <v>0.6329777075439798</v>
+        <v>88.94810439616614</v>
       </c>
       <c r="D36">
-        <v>82.74980143178919</v>
+        <v>103.1</v>
       </c>
       <c r="E36">
-        <v>66.31646700415607</v>
+        <v>3.32</v>
       </c>
       <c r="F36">
-        <v>100.8155134603174</v>
+        <v>861.1</v>
       </c>
       <c r="G36">
-        <v>0.8880139951017569</v>
+        <v>2.370695903486064</v>
       </c>
       <c r="H36">
-        <v>546.0972577444435</v>
+        <v>8.842968903161186</v>
       </c>
     </row>
   </sheetData>

--- a/descstatistics.xlsx
+++ b/descstatistics.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>2.614626865671642</v>
+        <v>2.612342062193126</v>
       </c>
       <c r="C6">
-        <v>0.1758363789598219</v>
+        <v>0.9691110662819854</v>
       </c>
       <c r="D6">
-        <v>2.614626865671642</v>
+        <v>2.53</v>
       </c>
       <c r="E6">
         <v>0.62</v>
@@ -530,850 +530,850 @@
         <v>5.1</v>
       </c>
       <c r="G6">
-        <v>1.677688986729673</v>
+        <v>0.3067659175116544</v>
       </c>
       <c r="H6">
-        <v>78.63264016031189</v>
+        <v>-0.3068665241273303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>SRV</t>
         </is>
       </c>
       <c r="B7">
-        <v>2.374303826170701</v>
+        <v>2.384301580468978e-05</v>
       </c>
       <c r="C7">
-        <v>0.09693288318660817</v>
+        <v>6.400912419732247e-05</v>
       </c>
       <c r="D7">
-        <v>2.374303826170701</v>
+        <v>2.384301580468978e-05</v>
       </c>
       <c r="E7">
-        <v>-0.35554626629975</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>8.002799820521171</v>
+        <v>0.00307344064376255</v>
       </c>
       <c r="G7">
-        <v>28.33814510505669</v>
+        <v>28.19205858071168</v>
       </c>
       <c r="H7">
-        <v>2075.014877489089</v>
+        <v>1078.706010132589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRV</t>
+          <t>GIPIO</t>
         </is>
       </c>
       <c r="B8">
-        <v>2.384301580468978e-05</v>
+        <v>0.0008649651169490651</v>
       </c>
       <c r="C8">
-        <v>6.400912419732247e-05</v>
+        <v>0.04097924807158492</v>
       </c>
       <c r="D8">
-        <v>2.384301580468978e-05</v>
+        <v>0.004216484401163458</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>-0.1980669999078872</v>
       </c>
       <c r="F8">
-        <v>0.00307344064376255</v>
+        <v>0.1247280674400151</v>
       </c>
       <c r="G8">
-        <v>28.19205858071168</v>
+        <v>-1.521082873805112</v>
       </c>
       <c r="H8">
-        <v>1078.706010132589</v>
+        <v>5.379602094102715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GOP</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.003324928540084873</v>
+        <v>0.002261912439508675</v>
       </c>
       <c r="C9">
-        <v>0.00147876698848723</v>
+        <v>0.001315411440519781</v>
       </c>
       <c r="D9">
-        <v>0.003324928540084873</v>
+        <v>0.002261912439508675</v>
       </c>
       <c r="E9">
-        <v>-0.05103452367423229</v>
+        <v>-0.003311574072685937</v>
       </c>
       <c r="F9">
-        <v>0.06399597774803385</v>
+        <v>0.01035808830139654</v>
       </c>
       <c r="G9">
-        <v>8.05437152932247</v>
+        <v>1.840556043205335</v>
       </c>
       <c r="H9">
-        <v>1108.442770022408</v>
+        <v>13.0722204498455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GIPIO</t>
+          <t>IPI</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.0009744698923681236</v>
+        <v>0.001989473225590499</v>
       </c>
       <c r="C10">
-        <v>0.007422668566711944</v>
+        <v>0.01468031024240105</v>
       </c>
       <c r="D10">
-        <v>0.0009744698923681236</v>
+        <v>0.00207390281077555</v>
       </c>
       <c r="E10">
-        <v>-0.1980669999078872</v>
+        <v>-0.103433827334549</v>
       </c>
       <c r="F10">
-        <v>0.1247280674400151</v>
+        <v>0.07405317149206574</v>
       </c>
       <c r="G10">
-        <v>-8.42351289988072</v>
+        <v>-2.194275935439943</v>
       </c>
       <c r="H10">
-        <v>253.3486039802916</v>
+        <v>21.71586169016525</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>UMP</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.002258696165461041</v>
+        <v>0.005305792178223116</v>
       </c>
       <c r="C11">
-        <v>0.0002374273055942652</v>
+        <v>0.1691346212585551</v>
       </c>
       <c r="D11">
-        <v>0.002258696165461041</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>-0.003311574072685937</v>
+        <v>-0.176470588235294</v>
       </c>
       <c r="F11">
-        <v>0.01035808830139654</v>
+        <v>2.34090909090909</v>
       </c>
       <c r="G11">
-        <v>10.12365532610226</v>
+        <v>12.89230310274559</v>
       </c>
       <c r="H11">
-        <v>487.0870200414472</v>
+        <v>175.1220610665509</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IPI</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.001947824668543269</v>
+        <v>125.8768805093046</v>
       </c>
       <c r="C12">
-        <v>0.002664339781292776</v>
+        <v>88.94810439616614</v>
       </c>
       <c r="D12">
-        <v>0.001947824668543269</v>
+        <v>103.1</v>
       </c>
       <c r="E12">
-        <v>-0.103433827334549</v>
+        <v>3.32</v>
       </c>
       <c r="F12">
-        <v>0.07405317149206574</v>
+        <v>861.1</v>
       </c>
       <c r="G12">
-        <v>-12.24642065682345</v>
+        <v>2.370695903486064</v>
       </c>
       <c r="H12">
-        <v>746.9851222140363</v>
+        <v>8.842968903161186</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UMP</t>
+          <t>bioenergyLCOE</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.00540493374766115</v>
+        <v>0.07142952061275019</v>
       </c>
       <c r="C13">
-        <v>0.03086065312370483</v>
+        <v>0.007990394985755097</v>
       </c>
       <c r="D13">
-        <v>0.00540493374766115</v>
+        <v>0.07142952061275019</v>
       </c>
       <c r="E13">
-        <v>-0.176470588235294</v>
+        <v>0.0553603321313858</v>
       </c>
       <c r="F13">
-        <v>2.34090909090909</v>
+        <v>0.08237511664628983</v>
       </c>
       <c r="G13">
-        <v>70.73369458948586</v>
+        <v>-0.5668047403907712</v>
       </c>
       <c r="H13">
-        <v>5352.863386482351</v>
+        <v>-0.627286136820064</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EEPH</t>
+          <t>geothermalLCOE</t>
         </is>
       </c>
       <c r="B14">
-        <v>91.76781538208495</v>
+        <v>0.06361238090448816</v>
       </c>
       <c r="C14">
-        <v>0.7917281122484185</v>
+        <v>0.01074394446519138</v>
       </c>
       <c r="D14">
-        <v>91.76781538208495</v>
+        <v>0.06411118060350418</v>
       </c>
       <c r="E14">
-        <v>74.61604611401472</v>
+        <v>0.05044528841972351</v>
       </c>
       <c r="F14">
-        <v>120.608959652287</v>
+        <v>0.08569453656673431</v>
       </c>
       <c r="G14">
-        <v>7.876707063092192</v>
+        <v>0.5603917177056327</v>
       </c>
       <c r="H14">
-        <v>584.9223233897566</v>
+        <v>-0.2504893762346896</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEMP</t>
+          <t>offshorewindLCOE</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.7095084190368652</v>
+        <v>0.1449531713343722</v>
       </c>
       <c r="C15">
-        <v>0.007400211348411915</v>
+        <v>0.04108319566859613</v>
       </c>
       <c r="D15">
-        <v>0.7095084190368652</v>
+        <v>0.1449531713343722</v>
       </c>
       <c r="E15">
-        <v>0.4656498432159424</v>
+        <v>0.0751669704914093</v>
       </c>
       <c r="F15">
-        <v>0.932927131652832</v>
+        <v>0.1975487768650055</v>
       </c>
       <c r="G15">
-        <v>1.504342534948598</v>
+        <v>-0.3412230357170561</v>
       </c>
       <c r="H15">
-        <v>635.189437187361</v>
+        <v>-1.38312253095009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>co2_per_capita</t>
+          <t>solarphotovoltaicLCOE</t>
         </is>
       </c>
       <c r="B16">
-        <v>4.74131253361702</v>
+        <v>0.2096672623215111</v>
       </c>
       <c r="C16">
-        <v>0.005528394541957961</v>
+        <v>0.1382595860876787</v>
       </c>
       <c r="D16">
-        <v>4.74131253361702</v>
+        <v>0.1794013977050781</v>
       </c>
       <c r="E16">
-        <v>4.497000217437744</v>
+        <v>0.04834553971886635</v>
       </c>
       <c r="F16">
-        <v>4.888000011444092</v>
+        <v>0.4171486794948578</v>
       </c>
       <c r="G16">
-        <v>-12.15935685502329</v>
+        <v>0.4735860214538116</v>
       </c>
       <c r="H16">
-        <v>1024.704864611302</v>
+        <v>-1.298227360894984</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>solarpv</t>
+          <t>concentratedsolarLCOE</t>
         </is>
       </c>
       <c r="B17">
-        <v>22276.375</v>
+        <v>0.2574648512721791</v>
       </c>
       <c r="C17">
-        <v>493.9586769050584</v>
+        <v>0.08447435645587922</v>
       </c>
       <c r="D17">
-        <v>22276.375</v>
+        <v>0.2488883286714554</v>
       </c>
       <c r="E17">
-        <v>1453</v>
+        <v>0.1066529899835587</v>
       </c>
       <c r="F17">
-        <v>36117</v>
+        <v>0.3580037951469421</v>
       </c>
       <c r="G17">
-        <v>-14.7892201020686</v>
+        <v>-0.2452468828877555</v>
       </c>
       <c r="H17">
-        <v>977.6665274796063</v>
+        <v>-1.095277645328188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>solarthermal</t>
+          <t>hydropowerLCOE</t>
         </is>
       </c>
       <c r="B18">
-        <v>7954.0625</v>
+        <v>0.04171380031883416</v>
       </c>
       <c r="C18">
-        <v>137.0049895933334</v>
+        <v>0.00417466671366833</v>
       </c>
       <c r="D18">
-        <v>7954.0625</v>
+        <v>0.04140857234597206</v>
       </c>
       <c r="E18">
-        <v>449</v>
+        <v>0.03656065836548805</v>
       </c>
       <c r="F18">
-        <v>11170</v>
+        <v>0.05072170868515968</v>
       </c>
       <c r="G18">
-        <v>-26.26711975642949</v>
+        <v>0.7927507860405604</v>
       </c>
       <c r="H18">
-        <v>1732.689460132794</v>
+        <v>-0.5173967801179828</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>solarpvthermalhybrid</t>
+          <t>onshorewindLCOE</t>
         </is>
       </c>
       <c r="B19">
-        <v>2159.875</v>
+        <v>0.07511338143950748</v>
       </c>
       <c r="C19">
-        <v>46.8398221471379</v>
+        <v>0.02321116934881398</v>
       </c>
       <c r="D19">
-        <v>2159.875</v>
+        <v>0.07511338143950748</v>
       </c>
       <c r="E19">
-        <v>90</v>
+        <v>0.03312336653470993</v>
       </c>
       <c r="F19">
-        <v>3825</v>
+        <v>0.102061465382576</v>
       </c>
       <c r="G19">
-        <v>-7.565700364620867</v>
+        <v>-0.3776458091359895</v>
       </c>
       <c r="H19">
-        <v>1058.196909928706</v>
+        <v>-1.156769106633621</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>AC_WIND_E</t>
         </is>
       </c>
       <c r="B20">
-        <v>9924.6875</v>
+        <v>316.1049508174295</v>
       </c>
       <c r="C20">
-        <v>178.9155693878757</v>
+        <v>159.8155727924601</v>
       </c>
       <c r="D20">
-        <v>9924.6875</v>
+        <v>316.1049508174295</v>
       </c>
       <c r="E20">
-        <v>775</v>
+        <v>80.27706999999999</v>
       </c>
       <c r="F20">
-        <v>13780</v>
+        <v>665.4131</v>
       </c>
       <c r="G20">
-        <v>-24.60018216429721</v>
+        <v>0.7743476814332433</v>
       </c>
       <c r="H20">
-        <v>1436.581507220444</v>
+        <v>-0.1544893847592594</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hydropower</t>
+          <t>AC_SOLAR_E</t>
         </is>
       </c>
       <c r="B21">
-        <v>2331.875</v>
+        <v>211.7288171547036</v>
       </c>
       <c r="C21">
-        <v>38.72657000677695</v>
+        <v>187.8014850184363</v>
       </c>
       <c r="D21">
-        <v>2331.875</v>
+        <v>156.6771</v>
       </c>
       <c r="E21">
-        <v>206</v>
+        <v>4.406489</v>
       </c>
       <c r="F21">
-        <v>3037</v>
+        <v>676.4082</v>
       </c>
       <c r="G21">
-        <v>-30.30868058014197</v>
+        <v>0.9542252006018669</v>
       </c>
       <c r="H21">
-        <v>1726.114487076653</v>
+        <v>0.09725642696468517</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>marineandtidal</t>
+          <t>AC_HYD_E</t>
         </is>
       </c>
       <c r="B22">
-        <v>1411.4375</v>
+        <v>170.1124756797838</v>
       </c>
       <c r="C22">
-        <v>22.71170133545747</v>
+        <v>183.8324887997964</v>
       </c>
       <c r="D22">
-        <v>1411.4375</v>
+        <v>170.1124756797838</v>
       </c>
       <c r="E22">
-        <v>116</v>
+        <v>-225.667</v>
       </c>
       <c r="F22">
-        <v>1814</v>
+        <v>454.2148</v>
       </c>
       <c r="G22">
-        <v>-30.00424012229628</v>
+        <v>-0.3501906969459265</v>
       </c>
       <c r="H22">
-        <v>1888.965241711528</v>
+        <v>-0.5216645949050061</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bioenergy</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="B23">
-        <v>7320.375</v>
+        <v>82.16735430643379</v>
       </c>
       <c r="C23">
-        <v>130.4139617854294</v>
+        <v>11.8015405555595</v>
       </c>
       <c r="D23">
-        <v>7320.375</v>
+        <v>82.16735430643379</v>
       </c>
       <c r="E23">
-        <v>253</v>
+        <v>66.31646700415607</v>
       </c>
       <c r="F23">
-        <v>9681</v>
+        <v>100.8155134603174</v>
       </c>
       <c r="G23">
-        <v>-27.04323329357048</v>
+        <v>0.1490585303935781</v>
       </c>
       <c r="H23">
-        <v>1619.925495147122</v>
+        <v>-1.375092310472011</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>geothermal</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B24">
-        <v>755.625</v>
+        <v>2.34931700520112</v>
       </c>
       <c r="C24">
-        <v>14.86829114702335</v>
+        <v>1.849456117594442</v>
       </c>
       <c r="D24">
-        <v>755.625</v>
+        <v>2.06933726526059</v>
       </c>
       <c r="E24">
-        <v>25</v>
+        <v>-0.35554626629975</v>
       </c>
       <c r="F24">
-        <v>1248</v>
+        <v>8.002799820521171</v>
       </c>
       <c r="G24">
-        <v>-12.33788482970295</v>
+        <v>1.52866945664929</v>
       </c>
       <c r="H24">
-        <v>1334.211534484704</v>
+        <v>2.805842747152844</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bioenergyLCOE</t>
+          <t>GOP</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.06962120408813159</v>
+        <v>0.004380493779399126</v>
       </c>
       <c r="C25">
-        <v>0.000380129891951757</v>
+        <v>0.02783480899363309</v>
       </c>
       <c r="D25">
-        <v>0.06962120408813159</v>
+        <v>0.003592942783470316</v>
       </c>
       <c r="E25">
-        <v>0.0553603321313858</v>
+        <v>-0.05103452367423229</v>
       </c>
       <c r="F25">
-        <v>0.08237511664628983</v>
+        <v>0.06399597774803385</v>
       </c>
       <c r="G25">
-        <v>-2.885864478249564</v>
+        <v>0.3491717330918344</v>
       </c>
       <c r="H25">
-        <v>1021.792595257817</v>
+        <v>0.1538799713937866</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>geothermalLCOE</t>
+          <t>EEPH</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.065447521480647</v>
+        <v>90.94171347708021</v>
       </c>
       <c r="C26">
-        <v>0.0003733123594546809</v>
+        <v>14.65218351021504</v>
       </c>
       <c r="D26">
-        <v>0.065447521480647</v>
+        <v>85.23122316875812</v>
       </c>
       <c r="E26">
-        <v>0.05044528841972351</v>
+        <v>74.61604611401472</v>
       </c>
       <c r="F26">
-        <v>0.08569453656673431</v>
+        <v>120.608959652287</v>
       </c>
       <c r="G26">
-        <v>10.78795156952699</v>
+        <v>0.5496164323612156</v>
       </c>
       <c r="H26">
-        <v>1990.893766438241</v>
+        <v>-1.1502259895728</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>offshorewindLCOE</t>
+          <t>TEMP</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.1334782298654318</v>
+        <v>0.7161802982402158</v>
       </c>
       <c r="C27">
-        <v>0.001843447812742883</v>
+        <v>0.1381726471549978</v>
       </c>
       <c r="D27">
-        <v>0.1334782298654318</v>
+        <v>0.7161802982402158</v>
       </c>
       <c r="E27">
-        <v>0.0751669704914093</v>
+        <v>0.4656498432159424</v>
       </c>
       <c r="F27">
-        <v>0.1975487768650055</v>
+        <v>0.932927131652832</v>
       </c>
       <c r="G27">
-        <v>2.197925868578704</v>
+        <v>-0.01455815839517162</v>
       </c>
       <c r="H27">
-        <v>754.6741312417042</v>
+        <v>-1.136200631100447</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>solarphotovoltaicLCOE</t>
+          <t>co2_per_capita</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.1541555915027857</v>
+        <v>4.748300974106428</v>
       </c>
       <c r="C28">
-        <v>0.004871540717400084</v>
+        <v>0.1013102864892346</v>
       </c>
       <c r="D28">
-        <v>0.1541555915027857</v>
+        <v>4.75</v>
       </c>
       <c r="E28">
-        <v>0.04834553971886635</v>
+        <v>4.497000217437744</v>
       </c>
       <c r="F28">
-        <v>0.4171486794948578</v>
+        <v>4.888000011444092</v>
       </c>
       <c r="G28">
-        <v>26.22890935725088</v>
+        <v>-0.8181650781524707</v>
       </c>
       <c r="H28">
-        <v>1678.832551711825</v>
+        <v>0.3799766772023605</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>concentratedsolarLCOE</t>
+          <t>solarpv</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.2305581656595071</v>
+        <v>23106.40154787617</v>
       </c>
       <c r="C29">
-        <v>0.003579862352672162</v>
+        <v>8742.533196866321</v>
       </c>
       <c r="D29">
-        <v>0.2305581656595071</v>
+        <v>24623</v>
       </c>
       <c r="E29">
-        <v>0.1066529899835587</v>
+        <v>1453</v>
       </c>
       <c r="F29">
-        <v>0.3580037951469421</v>
+        <v>36117</v>
       </c>
       <c r="G29">
-        <v>2.955677824349928</v>
+        <v>-0.9713201005719181</v>
       </c>
       <c r="H29">
-        <v>1030.808683612083</v>
+        <v>0.4360449796555015</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hydropowerLCOE</t>
+          <t>solarthermal</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.04247033502906561</v>
+        <v>8156.318574514039</v>
       </c>
       <c r="C30">
-        <v>0.0002058803470562588</v>
+        <v>2470.563387590315</v>
       </c>
       <c r="D30">
-        <v>0.04247033502906561</v>
+        <v>8330</v>
       </c>
       <c r="E30">
-        <v>0.03656065836548805</v>
+        <v>449</v>
       </c>
       <c r="F30">
-        <v>0.05072170868515968</v>
+        <v>11170</v>
       </c>
       <c r="G30">
-        <v>8.335920960256342</v>
+        <v>-1.697177188893677</v>
       </c>
       <c r="H30">
-        <v>923.586105233124</v>
+        <v>3.217909475375182</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>onshorewindLCOE</t>
+          <t>solarpvthermalhybrid</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.06790467258542776</v>
+        <v>2219.764218862491</v>
       </c>
       <c r="C31">
-        <v>0.0009962096110690834</v>
+        <v>857.7337655660501</v>
       </c>
       <c r="D31">
-        <v>0.06790467258542776</v>
+        <v>2219.764218862491</v>
       </c>
       <c r="E31">
-        <v>0.03312336653470993</v>
+        <v>90</v>
       </c>
       <c r="F31">
-        <v>0.102061465382576</v>
+        <v>3825</v>
       </c>
       <c r="G31">
-        <v>-0.9991611239017049</v>
+        <v>-0.5442826015446207</v>
       </c>
       <c r="H31">
-        <v>854.9708813145097</v>
+        <v>0.4164424299006564</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AC_WIND_E</t>
+          <t>hydropower</t>
         </is>
       </c>
       <c r="B32">
-        <v>305.1769217647059</v>
+        <v>2393.761339092873</v>
       </c>
       <c r="C32">
-        <v>8.762659601141614</v>
+        <v>690.8258593337293</v>
       </c>
       <c r="D32">
-        <v>305.1769217647059</v>
+        <v>2635</v>
       </c>
       <c r="E32">
-        <v>80.27706999999999</v>
+        <v>206</v>
       </c>
       <c r="F32">
-        <v>665.4131</v>
+        <v>3037</v>
       </c>
       <c r="G32">
-        <v>14.10859149369666</v>
+        <v>-1.976680943116061</v>
       </c>
       <c r="H32">
-        <v>988.0960300875448</v>
+        <v>3.47639647461623</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AC_SOLAR_E</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="B33">
-        <v>202.1321261764706</v>
+        <v>10224.9215262779</v>
       </c>
       <c r="C33">
-        <v>10.09321381973508</v>
+        <v>3167.302460513226</v>
       </c>
       <c r="D33">
-        <v>202.1321261764706</v>
+        <v>10756</v>
       </c>
       <c r="E33">
-        <v>4.406489</v>
+        <v>775</v>
       </c>
       <c r="F33">
-        <v>676.4082</v>
+        <v>13780</v>
       </c>
       <c r="G33">
-        <v>18.58079633804018</v>
+        <v>-1.61721859378957</v>
       </c>
       <c r="H33">
-        <v>1102.155273548304</v>
+        <v>2.38676961757737</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AC_HYD_E</t>
+          <t>marineandtidal</t>
         </is>
       </c>
       <c r="B34">
-        <v>174.3219188235294</v>
+        <v>1442.712203023758</v>
       </c>
       <c r="C34">
-        <v>9.674347097763933</v>
+        <v>412.7561016867151</v>
       </c>
       <c r="D34">
-        <v>174.3219188235294</v>
+        <v>1557</v>
       </c>
       <c r="E34">
-        <v>-225.667</v>
+        <v>116</v>
       </c>
       <c r="F34">
-        <v>454.2148</v>
+        <v>1814</v>
       </c>
       <c r="G34">
-        <v>-7.788702395170548</v>
+        <v>-1.905917616552776</v>
       </c>
       <c r="H34">
-        <v>895.3966891200999</v>
+        <v>3.660398321858901</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>bioenergy</t>
         </is>
       </c>
       <c r="B35">
-        <v>82.74980143178919</v>
+        <v>7457.082613390929</v>
       </c>
       <c r="C35">
-        <v>0.6329777075439798</v>
+        <v>2422.537037717932</v>
       </c>
       <c r="D35">
-        <v>82.74980143178919</v>
+        <v>8119</v>
       </c>
       <c r="E35">
-        <v>66.31646700415607</v>
+        <v>253</v>
       </c>
       <c r="F35">
-        <v>100.8155134603174</v>
+        <v>9681</v>
       </c>
       <c r="G35">
-        <v>0.8880139951017569</v>
+        <v>-1.649271038628035</v>
       </c>
       <c r="H35">
-        <v>546.0972577444435</v>
+        <v>2.263823564300015</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>geothermal</t>
         </is>
       </c>
       <c r="B36">
-        <v>125.8768805093046</v>
+        <v>775.2535997120231</v>
       </c>
       <c r="C36">
-        <v>88.94810439616614</v>
+        <v>271.4023517194685</v>
       </c>
       <c r="D36">
-        <v>103.1</v>
+        <v>775.2535997120231</v>
       </c>
       <c r="E36">
-        <v>3.32</v>
+        <v>25</v>
       </c>
       <c r="F36">
-        <v>861.1</v>
+        <v>1248</v>
       </c>
       <c r="G36">
-        <v>2.370695903486064</v>
+        <v>-0.8308882028339376</v>
       </c>
       <c r="H36">
-        <v>8.842968903161186</v>
+        <v>1.429291892204604</v>
       </c>
     </row>
   </sheetData>

--- a/descstatistics.xlsx
+++ b/descstatistics.xlsx
@@ -403,25 +403,25 @@
         </is>
       </c>
       <c r="B2">
-        <v>72.48673784104389</v>
+        <v>77.68315363881402</v>
       </c>
       <c r="C2">
-        <v>19.07535985182943</v>
+        <v>23.56198188439115</v>
       </c>
       <c r="D2">
-        <v>72.48673784104389</v>
+        <v>81.27</v>
       </c>
       <c r="E2">
-        <v>-36.98</v>
+        <v>26.19</v>
       </c>
       <c r="F2">
         <v>145.31</v>
       </c>
       <c r="G2">
-        <v>0.2085611299891787</v>
+        <v>-0.0899864527914547</v>
       </c>
       <c r="H2">
-        <v>0.6256291524543403</v>
+        <v>-0.7964864059637256</v>
       </c>
     </row>
     <row r="3">
@@ -431,25 +431,25 @@
         </is>
       </c>
       <c r="B3">
-        <v>4.050681925436526</v>
+        <v>4.431343858298036</v>
       </c>
       <c r="C3">
-        <v>1.694804638876356</v>
+        <v>2.09353716151923</v>
       </c>
       <c r="D3">
-        <v>4.050681925436526</v>
+        <v>3.86</v>
       </c>
       <c r="E3">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="F3">
-        <v>23.86</v>
+        <v>13.31</v>
       </c>
       <c r="G3">
-        <v>2.142281355574208</v>
+        <v>1.532620625230828</v>
       </c>
       <c r="H3">
-        <v>8.102852181239902</v>
+        <v>2.53808456293752</v>
       </c>
     </row>
     <row r="4">
@@ -459,249 +459,249 @@
         </is>
       </c>
       <c r="B4">
-        <v>96.79999068402343</v>
+        <v>83.11075475999012</v>
       </c>
       <c r="C4">
-        <v>50.06656605233171</v>
+        <v>27.29391963384611</v>
       </c>
       <c r="D4">
-        <v>96.79999068402343</v>
+        <v>78.30000305175781</v>
       </c>
       <c r="E4">
-        <v>38.45000076293945</v>
+        <v>43.40000152587891</v>
       </c>
       <c r="F4">
-        <v>439</v>
+        <v>211.1999969482422</v>
       </c>
       <c r="G4">
-        <v>3.404560722132067</v>
+        <v>1.221949682401844</v>
       </c>
       <c r="H4">
-        <v>14.27338956720185</v>
+        <v>2.307994614233706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>geothermal</t>
         </is>
       </c>
       <c r="B5">
-        <v>1.058587086013819</v>
+        <v>735.0331151328456</v>
       </c>
       <c r="C5">
-        <v>1.241492434419817</v>
+        <v>152.5960824802775</v>
       </c>
       <c r="D5">
-        <v>1.058587086013819</v>
+        <v>724</v>
       </c>
       <c r="E5">
-        <v>-0.05</v>
+        <v>378</v>
       </c>
       <c r="F5">
-        <v>5.28</v>
+        <v>1120</v>
       </c>
       <c r="G5">
-        <v>1.847343613604914</v>
+        <v>0.3428612771404437</v>
       </c>
       <c r="H5">
-        <v>3.085571339981716</v>
+        <v>0.4107387095657864</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTY</t>
+          <t>bioenergy</t>
         </is>
       </c>
       <c r="B6">
-        <v>2.612342062193126</v>
+        <v>8593.048517520216</v>
       </c>
       <c r="C6">
-        <v>0.9691110662819854</v>
+        <v>1207.330613175012</v>
       </c>
       <c r="D6">
-        <v>2.53</v>
+        <v>9008</v>
       </c>
       <c r="E6">
-        <v>0.62</v>
+        <v>4686</v>
       </c>
       <c r="F6">
-        <v>5.1</v>
+        <v>9681</v>
       </c>
       <c r="G6">
-        <v>0.3067659175116544</v>
+        <v>-1.360854473719958</v>
       </c>
       <c r="H6">
-        <v>-0.3068665241273303</v>
+        <v>1.02517478136332</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRV</t>
+          <t>marineandtidal</t>
         </is>
       </c>
       <c r="B7">
-        <v>2.384301580468978e-05</v>
+        <v>1611.134000770119</v>
       </c>
       <c r="C7">
-        <v>6.400912419732247e-05</v>
+        <v>248.2515882449749</v>
       </c>
       <c r="D7">
-        <v>2.384301580468978e-05</v>
+        <v>1696</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="F7">
-        <v>0.00307344064376255</v>
+        <v>1814</v>
       </c>
       <c r="G7">
-        <v>28.19205858071168</v>
+        <v>-1.534784749924318</v>
       </c>
       <c r="H7">
-        <v>1078.706010132589</v>
+        <v>1.526120423554205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GIPIO</t>
+          <t>hydropower</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.0008649651169490651</v>
+        <v>2468.99730458221</v>
       </c>
       <c r="C8">
-        <v>0.04097924807158492</v>
+        <v>468.7463294077681</v>
       </c>
       <c r="D8">
-        <v>0.004216484401163458</v>
+        <v>2674</v>
       </c>
       <c r="E8">
-        <v>-0.1980669999078872</v>
+        <v>1140</v>
       </c>
       <c r="F8">
-        <v>0.1247280674400151</v>
+        <v>2985</v>
       </c>
       <c r="G8">
-        <v>-1.521082873805112</v>
+        <v>-1.390411386833531</v>
       </c>
       <c r="H8">
-        <v>5.379602094102715</v>
+        <v>0.8212845534156896</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.002261912439508675</v>
+        <v>10432.43858298036</v>
       </c>
       <c r="C9">
-        <v>0.001315411440519781</v>
+        <v>2299.813379868937</v>
       </c>
       <c r="D9">
-        <v>0.002261912439508675</v>
+        <v>10756</v>
       </c>
       <c r="E9">
-        <v>-0.003311574072685937</v>
+        <v>4141</v>
       </c>
       <c r="F9">
-        <v>0.01035808830139654</v>
+        <v>13780</v>
       </c>
       <c r="G9">
-        <v>1.840556043205335</v>
+        <v>-1.029034071754668</v>
       </c>
       <c r="H9">
-        <v>13.0722204498455</v>
+        <v>0.2788855990106658</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IPI</t>
+          <t>solarpv</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.001989473225590499</v>
+        <v>22341.09703504043</v>
       </c>
       <c r="C10">
-        <v>0.01468031024240105</v>
+        <v>6890.612658112477</v>
       </c>
       <c r="D10">
-        <v>0.00207390281077555</v>
+        <v>24718</v>
       </c>
       <c r="E10">
-        <v>-0.103433827334549</v>
+        <v>6281</v>
       </c>
       <c r="F10">
-        <v>0.07405317149206574</v>
+        <v>33945</v>
       </c>
       <c r="G10">
-        <v>-2.194275935439943</v>
+        <v>-0.9284257171694875</v>
       </c>
       <c r="H10">
-        <v>21.71586169016525</v>
+        <v>-0.297433523073189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UMP</t>
+          <t>solarthermal</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.005305792178223116</v>
+        <v>8786.375818251829</v>
       </c>
       <c r="C11">
-        <v>0.1691346212585551</v>
+        <v>1916.468666564495</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>8557</v>
       </c>
       <c r="E11">
-        <v>-0.176470588235294</v>
+        <v>4063</v>
       </c>
       <c r="F11">
-        <v>2.34090909090909</v>
+        <v>11170</v>
       </c>
       <c r="G11">
-        <v>12.89230310274559</v>
+        <v>-0.6438116272685879</v>
       </c>
       <c r="H11">
-        <v>175.1220610665509</v>
+        <v>-0.2573422174111837</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>solarpvthermalhybrid</t>
         </is>
       </c>
       <c r="B12">
-        <v>125.8768805093046</v>
+        <v>2501.869464767039</v>
       </c>
       <c r="C12">
-        <v>88.94810439616614</v>
+        <v>716.7783875347288</v>
       </c>
       <c r="D12">
-        <v>103.1</v>
+        <v>2620</v>
       </c>
       <c r="E12">
-        <v>3.32</v>
+        <v>1007</v>
       </c>
       <c r="F12">
-        <v>861.1</v>
+        <v>3825</v>
       </c>
       <c r="G12">
-        <v>2.370695903486064</v>
+        <v>-0.1267510529860741</v>
       </c>
       <c r="H12">
-        <v>8.842968903161186</v>
+        <v>-0.3696395352862938</v>
       </c>
     </row>
     <row r="13">
@@ -711,25 +711,25 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.07142952061275019</v>
+        <v>0.07399779709086861</v>
       </c>
       <c r="C13">
-        <v>0.007990394985755097</v>
+        <v>0.008049678379270014</v>
       </c>
       <c r="D13">
-        <v>0.07142952061275019</v>
+        <v>0.07818926870822906</v>
       </c>
       <c r="E13">
-        <v>0.0553603321313858</v>
+        <v>0.05668433383107185</v>
       </c>
       <c r="F13">
         <v>0.08237511664628983</v>
       </c>
       <c r="G13">
-        <v>-0.5668047403907712</v>
+        <v>-1.03342044184946</v>
       </c>
       <c r="H13">
-        <v>-0.627286136820064</v>
+        <v>-0.1756407212525679</v>
       </c>
     </row>
     <row r="14">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.06361238090448816</v>
+        <v>0.06286671067149445</v>
       </c>
       <c r="C14">
-        <v>0.01074394446519138</v>
+        <v>0.01300038760278052</v>
       </c>
       <c r="D14">
         <v>0.06411118060350418</v>
@@ -754,10 +754,10 @@
         <v>0.08569453656673431</v>
       </c>
       <c r="G14">
-        <v>0.5603917177056327</v>
+        <v>0.706240093614962</v>
       </c>
       <c r="H14">
-        <v>-0.2504893762346896</v>
+        <v>-0.8140453447331817</v>
       </c>
     </row>
     <row r="15">
@@ -767,25 +767,25 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.1449531713343722</v>
+        <v>0.1703744733051286</v>
       </c>
       <c r="C15">
-        <v>0.04108319566859613</v>
+        <v>0.0251296343464092</v>
       </c>
       <c r="D15">
-        <v>0.1449531713343722</v>
+        <v>0.1721992492675781</v>
       </c>
       <c r="E15">
-        <v>0.0751669704914093</v>
+        <v>0.1061521768569946</v>
       </c>
       <c r="F15">
         <v>0.1975487768650055</v>
       </c>
       <c r="G15">
-        <v>-0.3412230357170561</v>
+        <v>-1.127550925303628</v>
       </c>
       <c r="H15">
-        <v>-1.38312253095009</v>
+        <v>0.1541401504579492</v>
       </c>
     </row>
     <row r="16">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.2096672623215111</v>
+        <v>0.2771395316916243</v>
       </c>
       <c r="C16">
-        <v>0.1382595860876787</v>
+        <v>0.1272946091598648</v>
       </c>
       <c r="D16">
-        <v>0.1794013977050781</v>
+        <v>0.2326332479715347</v>
       </c>
       <c r="E16">
-        <v>0.04834553971886635</v>
+        <v>0.08365974575281143</v>
       </c>
       <c r="F16">
         <v>0.4171486794948578</v>
       </c>
       <c r="G16">
-        <v>0.4735860214538116</v>
+        <v>-0.05059042338779202</v>
       </c>
       <c r="H16">
-        <v>-1.298227360894984</v>
+        <v>-1.692450871902903</v>
       </c>
     </row>
     <row r="17">
@@ -823,25 +823,25 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.2574648512721791</v>
+        <v>0.3045344701066217</v>
       </c>
       <c r="C17">
-        <v>0.08447435645587922</v>
+        <v>0.05985454455332963</v>
       </c>
       <c r="D17">
-        <v>0.2488883286714554</v>
+        <v>0.3375742137432098</v>
       </c>
       <c r="E17">
-        <v>0.1066529899835587</v>
+        <v>0.2062131762504578</v>
       </c>
       <c r="F17">
         <v>0.3580037951469421</v>
       </c>
       <c r="G17">
-        <v>-0.2452468828877555</v>
+        <v>-0.4410258176734782</v>
       </c>
       <c r="H17">
-        <v>-1.095277645328188</v>
+        <v>-1.668612275325621</v>
       </c>
     </row>
     <row r="18">
@@ -851,13 +851,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.04171380031883416</v>
+        <v>0.04015358510037362</v>
       </c>
       <c r="C18">
-        <v>0.00417466671366833</v>
+        <v>0.003597402830437535</v>
       </c>
       <c r="D18">
-        <v>0.04140857234597206</v>
+        <v>0.03888270631432533</v>
       </c>
       <c r="E18">
         <v>0.03656065836548805</v>
@@ -866,10 +866,10 @@
         <v>0.05072170868515968</v>
       </c>
       <c r="G18">
-        <v>0.7927507860405604</v>
+        <v>1.377488513229001</v>
       </c>
       <c r="H18">
-        <v>-0.5173967801179828</v>
+        <v>1.056352148218705</v>
       </c>
     </row>
     <row r="19">
@@ -879,53 +879,53 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.07511338143950748</v>
+        <v>0.0892627970801439</v>
       </c>
       <c r="C19">
-        <v>0.02321116934881398</v>
+        <v>0.01396466491589003</v>
       </c>
       <c r="D19">
-        <v>0.07511338143950748</v>
+        <v>0.0892062783241272</v>
       </c>
       <c r="E19">
-        <v>0.03312336653470993</v>
+        <v>0.05995915830135345</v>
       </c>
       <c r="F19">
         <v>0.102061465382576</v>
       </c>
       <c r="G19">
-        <v>-0.3776458091359895</v>
+        <v>-0.7278759465804223</v>
       </c>
       <c r="H19">
-        <v>-1.156769106633621</v>
+        <v>-0.8963410330017543</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AC_WIND_E</t>
+          <t>AC_HYD_E</t>
         </is>
       </c>
       <c r="B20">
-        <v>316.1049508174295</v>
+        <v>212.6154013015017</v>
       </c>
       <c r="C20">
-        <v>159.8155727924601</v>
+        <v>185.0673506072122</v>
       </c>
       <c r="D20">
-        <v>316.1049508174295</v>
+        <v>211.5381</v>
       </c>
       <c r="E20">
-        <v>80.27706999999999</v>
+        <v>-88.47949</v>
       </c>
       <c r="F20">
-        <v>665.4131</v>
+        <v>454.2148</v>
       </c>
       <c r="G20">
-        <v>0.7743476814332433</v>
+        <v>-0.3247057354140341</v>
       </c>
       <c r="H20">
-        <v>-0.1544893847592594</v>
+        <v>-1.171661044087131</v>
       </c>
     </row>
     <row r="21">
@@ -935,53 +935,53 @@
         </is>
       </c>
       <c r="B21">
-        <v>211.7288171547036</v>
+        <v>88.36187717751251</v>
       </c>
       <c r="C21">
-        <v>187.8014850184363</v>
+        <v>68.15393449774979</v>
       </c>
       <c r="D21">
-        <v>156.6771</v>
+        <v>97.26361</v>
       </c>
       <c r="E21">
         <v>4.406489</v>
       </c>
       <c r="F21">
-        <v>676.4082</v>
+        <v>306.3724</v>
       </c>
       <c r="G21">
-        <v>0.9542252006018669</v>
+        <v>0.5487075462674034</v>
       </c>
       <c r="H21">
-        <v>0.09725642696468517</v>
+        <v>-0.2155657903324575</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AC_HYD_E</t>
+          <t>AC_WIND_E</t>
         </is>
       </c>
       <c r="B22">
-        <v>170.1124756797838</v>
+        <v>220.8265674393531</v>
       </c>
       <c r="C22">
-        <v>183.8324887997964</v>
+        <v>82.62062584145272</v>
       </c>
       <c r="D22">
-        <v>170.1124756797838</v>
+        <v>238.9279</v>
       </c>
       <c r="E22">
-        <v>-225.667</v>
+        <v>80.27706999999999</v>
       </c>
       <c r="F22">
-        <v>454.2148</v>
+        <v>462.2576</v>
       </c>
       <c r="G22">
-        <v>-0.3501906969459265</v>
+        <v>0.3555322566680399</v>
       </c>
       <c r="H22">
-        <v>-0.5216645949050061</v>
+        <v>-0.5181545670550851</v>
       </c>
     </row>
     <row r="23">
@@ -991,81 +991,81 @@
         </is>
       </c>
       <c r="B23">
-        <v>82.16735430643379</v>
+        <v>89.2364781837186</v>
       </c>
       <c r="C23">
-        <v>11.8015405555595</v>
+        <v>8.818607687117936</v>
       </c>
       <c r="D23">
-        <v>82.16735430643379</v>
+        <v>92.86022947458119</v>
       </c>
       <c r="E23">
-        <v>66.31646700415607</v>
+        <v>75.36663303469656</v>
       </c>
       <c r="F23">
         <v>100.8155134603174</v>
       </c>
       <c r="G23">
-        <v>0.1490585303935781</v>
+        <v>-0.3381009333581625</v>
       </c>
       <c r="H23">
-        <v>-1.375092310472011</v>
+        <v>-1.149697808954601</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="B24">
-        <v>2.34931700520112</v>
+        <v>108.5987485560262</v>
       </c>
       <c r="C24">
-        <v>1.849456117594442</v>
+        <v>69.43487660831566</v>
       </c>
       <c r="D24">
-        <v>2.06933726526059</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="E24">
-        <v>-0.35554626629975</v>
+        <v>3.32</v>
       </c>
       <c r="F24">
-        <v>8.002799820521171</v>
+        <v>626.03</v>
       </c>
       <c r="G24">
-        <v>1.52866945664929</v>
+        <v>1.72246057147613</v>
       </c>
       <c r="H24">
-        <v>2.805842747152844</v>
+        <v>5.110708455908691</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GOP</t>
+          <t>TEMP</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.004380493779399126</v>
+        <v>0.6523298377204868</v>
       </c>
       <c r="C25">
-        <v>0.02783480899363309</v>
+        <v>0.1311435913626759</v>
       </c>
       <c r="D25">
-        <v>0.003592942783470316</v>
+        <v>0.5967816710472107</v>
       </c>
       <c r="E25">
-        <v>-0.05103452367423229</v>
+        <v>0.4656498432159424</v>
       </c>
       <c r="F25">
-        <v>0.06399597774803385</v>
+        <v>0.932927131652832</v>
       </c>
       <c r="G25">
-        <v>0.3491717330918344</v>
+        <v>0.8453411697151439</v>
       </c>
       <c r="H25">
-        <v>0.1538799713937866</v>
+        <v>-0.1369735257770444</v>
       </c>
     </row>
     <row r="26">
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="B26">
-        <v>90.94171347708021</v>
+        <v>97.91587014638806</v>
       </c>
       <c r="C26">
-        <v>14.65218351021504</v>
+        <v>14.40559448249657</v>
       </c>
       <c r="D26">
-        <v>85.23122316875812</v>
+        <v>104.8332031540361</v>
       </c>
       <c r="E26">
         <v>74.61604611401472</v>
@@ -1090,290 +1090,290 @@
         <v>120.608959652287</v>
       </c>
       <c r="G26">
-        <v>0.5496164323612156</v>
+        <v>-0.2214956036214797</v>
       </c>
       <c r="H26">
-        <v>-1.1502259895728</v>
+        <v>-1.207829495316854</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TEMP</t>
+          <t>co2_per_capita</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.7161802982402158</v>
+        <v>4.770958447483902</v>
       </c>
       <c r="C27">
-        <v>0.1381726471549978</v>
+        <v>0.09729304318075166</v>
       </c>
       <c r="D27">
-        <v>0.7161802982402158</v>
+        <v>4.776000022888184</v>
       </c>
       <c r="E27">
-        <v>0.4656498432159424</v>
+        <v>4.576000213623047</v>
       </c>
       <c r="F27">
-        <v>0.932927131652832</v>
+        <v>4.888000011444092</v>
       </c>
       <c r="G27">
-        <v>-0.01455815839517162</v>
+        <v>-0.5313966298451945</v>
       </c>
       <c r="H27">
-        <v>-1.136200631100447</v>
+        <v>-0.7147490017377058</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>co2_per_capita</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="B28">
-        <v>4.748300974106428</v>
+        <v>0.742329611089719</v>
       </c>
       <c r="C28">
-        <v>0.1013102864892346</v>
+        <v>1.439771131584981</v>
       </c>
       <c r="D28">
-        <v>4.75</v>
+        <v>0.11</v>
       </c>
       <c r="E28">
-        <v>4.497000217437744</v>
+        <v>-0.02</v>
       </c>
       <c r="F28">
-        <v>4.888000011444092</v>
+        <v>5.05</v>
       </c>
       <c r="G28">
-        <v>-0.8181650781524707</v>
+        <v>2.148255687345931</v>
       </c>
       <c r="H28">
-        <v>0.3799766772023605</v>
+        <v>3.092828842764789</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>solarpv</t>
+          <t>LTY</t>
         </is>
       </c>
       <c r="B29">
-        <v>23106.40154787617</v>
+        <v>2.830808625336927</v>
       </c>
       <c r="C29">
-        <v>8742.533196866321</v>
+        <v>0.9234339806382358</v>
       </c>
       <c r="D29">
-        <v>24623</v>
+        <v>2.62</v>
       </c>
       <c r="E29">
-        <v>1453</v>
+        <v>1.5</v>
       </c>
       <c r="F29">
-        <v>36117</v>
+        <v>5.1</v>
       </c>
       <c r="G29">
-        <v>-0.9713201005719181</v>
+        <v>0.6113309352719118</v>
       </c>
       <c r="H29">
-        <v>0.4360449796555015</v>
+        <v>-0.6095245421775979</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>solarthermal</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B30">
-        <v>8156.318574514039</v>
+        <v>1.731617321779386</v>
       </c>
       <c r="C30">
-        <v>2470.563387590315</v>
+        <v>1.173492717597083</v>
       </c>
       <c r="D30">
-        <v>8330</v>
+        <v>1.64004344238989</v>
       </c>
       <c r="E30">
-        <v>449</v>
+        <v>-0.35554626629975</v>
       </c>
       <c r="F30">
-        <v>11170</v>
+        <v>3.83910029665101</v>
       </c>
       <c r="G30">
-        <v>-1.697177188893677</v>
+        <v>-0.03153219098966943</v>
       </c>
       <c r="H30">
-        <v>3.217909475375182</v>
+        <v>-0.4706033749728156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>solarpvthermalhybrid</t>
+          <t>SRV</t>
         </is>
       </c>
       <c r="B31">
-        <v>2219.764218862491</v>
+        <v>5.621700612538196e-06</v>
       </c>
       <c r="C31">
-        <v>857.7337655660501</v>
+        <v>1.589664337473419e-05</v>
       </c>
       <c r="D31">
-        <v>2219.764218862491</v>
+        <v>2.066540280067681e-06</v>
       </c>
       <c r="E31">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>3825</v>
+        <v>0.0003049771922516432</v>
       </c>
       <c r="G31">
-        <v>-0.5442826015446207</v>
+        <v>9.236170774892264</v>
       </c>
       <c r="H31">
-        <v>0.4164424299006564</v>
+        <v>124.5591270877064</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hydropower</t>
+          <t>GOP</t>
         </is>
       </c>
       <c r="B32">
-        <v>2393.761339092873</v>
+        <v>0.00494702970974812</v>
       </c>
       <c r="C32">
-        <v>690.8258593337293</v>
+        <v>0.0267552441494485</v>
       </c>
       <c r="D32">
-        <v>2635</v>
+        <v>0.003592942783470316</v>
       </c>
       <c r="E32">
-        <v>206</v>
+        <v>-0.05103452367423229</v>
       </c>
       <c r="F32">
-        <v>3037</v>
+        <v>0.05672762444892714</v>
       </c>
       <c r="G32">
-        <v>-1.976680943116061</v>
+        <v>-0.2404131976370456</v>
       </c>
       <c r="H32">
-        <v>3.47639647461623</v>
+        <v>0.2780536704796872</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>GIPIO</t>
         </is>
       </c>
       <c r="B33">
-        <v>10224.9215262779</v>
+        <v>-0.0002605415705437459</v>
       </c>
       <c r="C33">
-        <v>3167.302460513226</v>
+        <v>0.03652510616508196</v>
       </c>
       <c r="D33">
-        <v>10756</v>
+        <v>0.002933670944749839</v>
       </c>
       <c r="E33">
-        <v>775</v>
+        <v>-0.1615015605329002</v>
       </c>
       <c r="F33">
-        <v>13780</v>
+        <v>0.06382623700025461</v>
       </c>
       <c r="G33">
-        <v>-1.61721859378957</v>
+        <v>-1.50573976705967</v>
       </c>
       <c r="H33">
-        <v>2.38676961757737</v>
+        <v>3.819008694668942</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>marineandtidal</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B34">
-        <v>1442.712203023758</v>
+        <v>0.002247380141967199</v>
       </c>
       <c r="C34">
-        <v>412.7561016867151</v>
+        <v>0.001659126855442367</v>
       </c>
       <c r="D34">
-        <v>1557</v>
+        <v>0.002051695730114396</v>
       </c>
       <c r="E34">
-        <v>116</v>
+        <v>-0.003311574072685937</v>
       </c>
       <c r="F34">
-        <v>1814</v>
+        <v>0.01035808830139654</v>
       </c>
       <c r="G34">
-        <v>-1.905917616552776</v>
+        <v>1.433432724169902</v>
       </c>
       <c r="H34">
-        <v>3.660398321858901</v>
+        <v>6.9554239012985</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bioenergy</t>
+          <t>IPI</t>
         </is>
       </c>
       <c r="B35">
-        <v>7457.082613390929</v>
+        <v>0.00207512288297618</v>
       </c>
       <c r="C35">
-        <v>2422.537037717932</v>
+        <v>0.01313534493148389</v>
       </c>
       <c r="D35">
-        <v>8119</v>
+        <v>0.001724364666710812</v>
       </c>
       <c r="E35">
-        <v>253</v>
+        <v>-0.103433827334549</v>
       </c>
       <c r="F35">
-        <v>9681</v>
+        <v>0.07405317149206574</v>
       </c>
       <c r="G35">
-        <v>-1.649271038628035</v>
+        <v>-2.107488877997219</v>
       </c>
       <c r="H35">
-        <v>2.263823564300015</v>
+        <v>33.83323000790475</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>geothermal</t>
+          <t>UMP</t>
         </is>
       </c>
       <c r="B36">
-        <v>775.2535997120231</v>
+        <v>0.0002852308587351054</v>
       </c>
       <c r="C36">
-        <v>271.4023517194685</v>
+        <v>0.02874970347454425</v>
       </c>
       <c r="D36">
-        <v>775.2535997120231</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>25</v>
+        <v>-0.07462686567164178</v>
       </c>
       <c r="F36">
-        <v>1248</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="G36">
-        <v>-0.8308882028339376</v>
+        <v>0.4263353794357424</v>
       </c>
       <c r="H36">
-        <v>1.429291892204604</v>
+        <v>0.244746189032619</v>
       </c>
     </row>
   </sheetData>
